--- a/backend/scripts/test_gstr1_final.xlsx
+++ b/backend/scripts/test_gstr1_final.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="68">
   <si>
     <t>GSTIN/UIN of Recipient</t>
   </si>
@@ -152,6 +152,12 @@
     <t>Type</t>
   </si>
   <si>
+    <t>OE</t>
+  </si>
+  <si>
+    <t>27-Chandigarh</t>
+  </si>
+  <si>
     <t>HSN</t>
   </si>
   <si>
@@ -183,6 +189,18 @@
   </si>
   <si>
     <t>NOS</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>JUTD15N 20V750MA</t>
+  </si>
+  <si>
+    <t>NOS-NUMBERS</t>
+  </si>
+  <si>
+    <t>TEST ITEM 2</t>
   </si>
   <si>
     <t>Nature of Document</t>
@@ -1104,7 +1122,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1139,6 +1157,52 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2">
+        <v>18</v>
+      </c>
+      <c r="E2">
+        <v>111400</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3">
+        <v>18</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1147,7 +1211,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1160,31 +1224,31 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F1" t="s">
         <v>11</v>
       </c>
       <c r="G1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J1" t="s">
         <v>12</v>
@@ -1192,33 +1256,97 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D2">
-        <v>357</v>
+        <v>387</v>
       </c>
       <c r="E2">
-        <v>270574</v>
+        <v>272226</v>
       </c>
       <c r="F2">
-        <v>229300</v>
+        <v>230700</v>
       </c>
       <c r="G2">
         <v>40077</v>
       </c>
       <c r="H2">
-        <v>598.5</v>
+        <v>724.5</v>
       </c>
       <c r="I2">
-        <v>598.5</v>
+        <v>724.5</v>
       </c>
       <c r="J2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <v>118</v>
+      </c>
+      <c r="F3">
+        <v>100</v>
+      </c>
+      <c r="G3">
+        <v>18</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4">
+        <v>11</v>
+      </c>
+      <c r="E4">
+        <v>129800</v>
+      </c>
+      <c r="F4">
+        <v>110000</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>9900</v>
+      </c>
+      <c r="I4">
+        <v>9900</v>
+      </c>
+      <c r="J4">
         <v>0</v>
       </c>
     </row>
@@ -1240,24 +1368,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
@@ -1266,7 +1394,7 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E2">
         <v>0</v>
